--- a/assignment/assignment5/shorter_WBS.xlsx
+++ b/assignment/assignment5/shorter_WBS.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>US-01 Upload an event export as-is (UP-01 – UP-14, UP-19)</t>
+          <t>User story: As staff, I can upload an event's export file as-is</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>CampusGroups and 12twenty adapters; detect the format from the headers</t>
+          <t>Read CampusGroups and 12twenty files; detect which platform a file came from</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>Duplicate-file protection and commit</t>
+          <t>Block the same file from being imported twice; save the import</t>
         </is>
       </c>
       <c r="C18" s="18" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>Tests: A1 (293 rows, 79 NetIDs) and A2 (a re-upload adds nothing)</t>
+          <t>Tests: the sample files give 293 rows and 79 unique students; a re-upload adds nothing</t>
         </is>
       </c>
       <c r="C20" s="18" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>US-02 Link the same person across events (UP-15, UP-16)</t>
+          <t>User story: As staff, I see the same person linked across events</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="B22" s="26" t="inlineStr">
         <is>
-          <t>Identity linker (NetID, then email) and data-quality flags</t>
+          <t>Match people by NetID, then by email; flag uncertain matches</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B23" s="26" t="inlineStr">
         <is>
-          <t>Tests for the linker cases</t>
+          <t>Tests for the matching cases</t>
         </is>
       </c>
       <c r="C23" s="18" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>US-03 Ask a question and see the SQL and the table (CH-01 – CH-22)</t>
+          <t>User story: As staff, I can ask a question in plain English and see the SQL and the result table</t>
         </is>
       </c>
       <c r="C24" s="18" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B25" s="26" t="inlineStr">
         <is>
-          <t>Chat graph and prompt, with follow-ups, clarifying questions and repairs</t>
+          <t>AI pipeline from question to SQL, with follow-up questions, clarifying questions and error repair</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="B26" s="26" t="inlineStr">
         <is>
-          <t>SQL guard: one read-only SELECT on one view</t>
+          <t>SQL guard: allow only one read-only SELECT on one view</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B29" s="26" t="inlineStr">
         <is>
-          <t>Tests: A6 privacy and A8 harmful SQL</t>
+          <t>Tests: no student data reaches the AI when sharing is off; harmful SQL is blocked</t>
         </is>
       </c>
       <c r="C29" s="18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>US-04 Manage AI models and result sharing (ST-01 – ST-10, CH-08, CH-09)</t>
+          <t>User story: As staff, I can choose the AI model and decide whether it may see query results</t>
         </is>
       </c>
       <c r="C30" s="18" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B31" s="26" t="inlineStr">
         <is>
-          <t>Encrypted AI model profiles, Test connection, sharing rules</t>
+          <t>AI model settings with encrypted keys, a Test connection button and sharing rules</t>
         </is>
       </c>
       <c r="C31" s="18" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B32" s="26" t="inlineStr">
         <is>
-          <t>Settings page and the share switch</t>
+          <t>Settings page and the per-question sharing switch</t>
         </is>
       </c>
       <c r="C32" s="18" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>US-05 Download results and see what was imported (CH-05, CH-06, DS-01 – DS-05)</t>
+          <t>User story: As staff, I can download results as Excel or CSV and see what was imported</t>
         </is>
       </c>
       <c r="C33" s="18" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B34" s="26" t="inlineStr">
         <is>
-          <t>Excel and CSV export with a formula guard; full-dataset export</t>
+          <t>Excel and CSV export, safe against formula injection; whole-dataset export</t>
         </is>
       </c>
       <c r="C34" s="18" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>MVP verification against the MOV (A1 – A10)</t>
+          <t>MVP verification against the MOV and the acceptance tests</t>
         </is>
       </c>
       <c r="C36" s="18" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>Chatbot benchmark: 20 questions and 10 held-out</t>
+          <t>Chatbot benchmark: 20 sponsor-style questions, plus 10 held-out questions</t>
         </is>
       </c>
       <c r="C37" s="18" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>Acceptance run and question-to-Excel timing (A10)</t>
+          <t>Run all acceptance tests; time a question to a downloaded Excel file</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>Walk the user stories and the sponsor's Oct 21 requests</t>
+          <t>Try every user story by hand, plus the sponsor's Oct 21 requests</t>
         </is>
       </c>
       <c r="C39" s="18" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B42" s="26" t="inlineStr">
         <is>
-          <t>Verify the ZotGPT gateway (by Oct 28)</t>
+          <t>Check that UCI's ZotGPT AI service works with the Hub (by Oct 28)</t>
         </is>
       </c>
       <c r="C42" s="18" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B43" s="26" t="inlineStr">
         <is>
-          <t>Send the sponsor the LLM credit request</t>
+          <t>Send the sponsor the request for AI usage credits</t>
         </is>
       </c>
       <c r="C43" s="18" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B52" s="25" t="inlineStr">
         <is>
-          <t>Milestone: MVP passes A1–A10 except A7 (Oct 22); midterm delivered</t>
+          <t>Milestone: MVP passes every acceptance test except staff login (Oct 22); midterm delivered</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>Sprint 2: Sponsor Demo and Backlog  |  Nov 3 – Nov 16  |  Planned</t>
+          <t>Sprint 2: Sponsor Demo and Follow-up Features  |  Nov 3 – Nov 16  |  Planned</t>
         </is>
       </c>
       <c r="B53" s="20" t="n"/>
@@ -1834,7 +1834,7 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>B4 Warn when an event is uploaded twice; delete a committed import</t>
+          <t>Warn when an event is uploaded twice; delete a saved import</t>
         </is>
       </c>
       <c r="C57" s="18" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B58" s="26" t="inlineStr">
         <is>
-          <t>Detect an existing event; replace or delete its rows</t>
+          <t>Detect an event already in the dataset; replace or delete its rows</t>
         </is>
       </c>
       <c r="C58" s="18" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="B60" s="23" t="inlineStr">
         <is>
-          <t>B1 Delete a conversation and set a retention period</t>
+          <t>Delete a chat conversation; set how long chats are kept</t>
         </is>
       </c>
       <c r="C60" s="18" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>Delete API and cleanup job</t>
+          <t>Delete API and automatic cleanup of old chats</t>
         </is>
       </c>
       <c r="C61" s="18" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B62" s="26" t="inlineStr">
         <is>
-          <t>Retention setting table</t>
+          <t>Database table for the retention setting</t>
         </is>
       </c>
       <c r="C62" s="18" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B63" s="26" t="inlineStr">
         <is>
-          <t>Delete button and retention choice</t>
+          <t>Delete button and retention choice in Settings</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B64" s="23" t="inlineStr">
         <is>
-          <t>B2 Downloads page for AI results</t>
+          <t>Downloads page that lists past AI results</t>
         </is>
       </c>
       <c r="C64" s="18" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="B65" s="26" t="inlineStr">
         <is>
-          <t>API that lists answers</t>
+          <t>API that lists past results</t>
         </is>
       </c>
       <c r="C65" s="18" t="inlineStr">
@@ -2075,7 +2075,7 @@
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>B3 Insights button on the Dataset page</t>
+          <t>Insights button on the Dataset page (preset questions)</t>
         </is>
       </c>
       <c r="C67" s="18" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="B68" s="26" t="inlineStr">
         <is>
-          <t>Preset questions; re-run the benchmark</t>
+          <t>Preset questions; re-run the chatbot benchmark</t>
         </is>
       </c>
       <c r="C68" s="18" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>Regression walk and user guide update</t>
+          <t>Regression check and user guide update</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>Milestone: sponsor demo given; B1–B4 done</t>
+          <t>Milestone: sponsor demo given; the four follow-up features done</t>
         </is>
       </c>
       <c r="C75" s="18" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>Staff login (acceptance test A7)</t>
+          <t>Staff login (the one acceptance test not yet passing)</t>
         </is>
       </c>
       <c r="C77" s="18" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B78" s="26" t="inlineStr">
         <is>
-          <t>Login backend and the A7 test</t>
+          <t>Login backend and its acceptance test</t>
         </is>
       </c>
       <c r="C78" s="18" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="B80" s="23" t="inlineStr">
         <is>
-          <t>CI and installation at the GPSRC</t>
+          <t>Automated testing (CI) and installation at the GPSRC</t>
         </is>
       </c>
       <c r="C80" s="18" t="inlineStr">
@@ -2395,7 +2395,7 @@
       </c>
       <c r="B81" s="26" t="inlineStr">
         <is>
-          <t>GitHub Actions CI</t>
+          <t>GitHub Actions CI: run the tests on every change</t>
         </is>
       </c>
       <c r="C81" s="18" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="B87" s="26" t="inlineStr">
         <is>
-          <t>Final acceptance run and benchmark</t>
+          <t>Final acceptance test run and chatbot benchmark</t>
         </is>
       </c>
       <c r="C87" s="18" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="B88" s="26" t="inlineStr">
         <is>
-          <t>Regression walk and bug fixes</t>
+          <t>Regression check and bug fixes</t>
         </is>
       </c>
       <c r="C88" s="18" t="inlineStr">
